--- a/output/graficos_educacion_tasas/comunal_e_mat_a_2020_metropolitana.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_mat_a_2020_metropolitana.xlsx
@@ -177,7 +177,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:35</t>
+    <t xml:space="preserve">2026-09-09 20:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_mat_a_2020_metropolitana.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_mat_a_2020_metropolitana.xlsx
@@ -24,150 +24,150 @@
     <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
+    <t xml:space="preserve">Santiago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerrillos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerro Navia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conchalí</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Bosque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huechuraba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Independencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Cisterna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Florida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Granja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Pintana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Reina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Barnechea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Espejo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Prado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Macul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maipú</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ñuñoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedro Aguirre Cerda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peñalolén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pudahuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilicura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinta Normal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recoleta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Joaquín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Miguel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Ramón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puente Alto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pirque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San José de Maipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lampa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiltil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Bernardo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calera de Tango</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melipilla</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alhué</t>
   </si>
   <si>
-    <t xml:space="preserve">Buin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calera de Tango</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerrillos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerro Navia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conchalí</t>
-  </si>
-  <si>
     <t xml:space="preserve">Curacaví</t>
   </si>
   <si>
-    <t xml:space="preserve">El Bosque</t>
+    <t xml:space="preserve">María Pinto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Pedro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talagante</t>
   </si>
   <si>
     <t xml:space="preserve">El Monte</t>
   </si>
   <si>
-    <t xml:space="preserve">Huechuraba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Independencia</t>
-  </si>
-  <si>
     <t xml:space="preserve">Isla de Maipo</t>
   </si>
   <si>
-    <t xml:space="preserve">La Cisterna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Florida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Granja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Pintana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Reina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lampa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lo Barnechea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lo Espejo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lo Prado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Macul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maipú</t>
-  </si>
-  <si>
-    <t xml:space="preserve">María Pinto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melipilla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ñuñoa</t>
-  </si>
-  <si>
     <t xml:space="preserve">Padre Hurtado</t>
   </si>
   <si>
-    <t xml:space="preserve">Paine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pedro Aguirre Cerda</t>
-  </si>
-  <si>
     <t xml:space="preserve">Peñaflor</t>
   </si>
   <si>
-    <t xml:space="preserve">Peñalolén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pirque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pudahuel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puente Alto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quilicura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quinta Normal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recoleta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Bernardo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Joaquín</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San José de Maipo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Miguel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Pedro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Ramón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santiago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talagante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiltil</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -177,7 +177,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:37</t>
+    <t xml:space="preserve">2026-09-18 10:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -589,7 +589,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>69.8</v>
+        <v>59.64</v>
       </c>
     </row>
     <row r="3">
@@ -597,7 +597,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>74.04</v>
+        <v>73.03</v>
       </c>
     </row>
     <row r="4">
@@ -605,7 +605,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>72.61</v>
+        <v>69.21</v>
       </c>
     </row>
     <row r="5">
@@ -613,7 +613,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>73.03</v>
+        <v>70.6</v>
       </c>
     </row>
     <row r="6">
@@ -621,7 +621,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>69.21</v>
+        <v>71.99</v>
       </c>
     </row>
     <row r="7">
@@ -629,7 +629,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>78.42</v>
+        <v>79.03</v>
       </c>
     </row>
     <row r="8">
@@ -637,7 +637,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>70.6</v>
+        <v>58.23</v>
       </c>
     </row>
     <row r="9">
@@ -645,7 +645,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>74.68</v>
+        <v>71.79</v>
       </c>
     </row>
     <row r="10">
@@ -653,7 +653,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>71.99</v>
+        <v>75.58</v>
       </c>
     </row>
     <row r="11">
@@ -661,7 +661,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>72.98</v>
+        <v>72.17</v>
       </c>
     </row>
     <row r="12">
@@ -669,7 +669,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>79.03</v>
+        <v>71.69</v>
       </c>
     </row>
     <row r="13">
@@ -677,7 +677,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>58.23</v>
+        <v>84.85</v>
       </c>
     </row>
     <row r="14">
@@ -685,7 +685,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>74.17</v>
+        <v>87.68</v>
       </c>
     </row>
     <row r="15">
@@ -693,7 +693,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>71.79</v>
+        <v>68.72</v>
       </c>
     </row>
     <row r="16">
@@ -701,7 +701,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>75.58</v>
+        <v>70.41</v>
       </c>
     </row>
     <row r="17">
@@ -709,7 +709,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>72.17</v>
+        <v>74.74</v>
       </c>
     </row>
     <row r="18">
@@ -717,7 +717,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>71.69</v>
+        <v>76.32</v>
       </c>
     </row>
     <row r="19">
@@ -725,7 +725,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>84.85</v>
+        <v>79.56</v>
       </c>
     </row>
     <row r="20">
@@ -733,7 +733,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>73.53</v>
+        <v>72.15</v>
       </c>
     </row>
     <row r="21">
@@ -741,7 +741,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>87.68</v>
+        <v>76.57</v>
       </c>
     </row>
     <row r="22">
@@ -749,7 +749,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>68.72</v>
+        <v>74.22</v>
       </c>
     </row>
     <row r="23">
@@ -757,7 +757,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>70.41</v>
+        <v>72.91</v>
       </c>
     </row>
     <row r="24">
@@ -765,7 +765,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>74.74</v>
+        <v>67.04</v>
       </c>
     </row>
     <row r="25">
@@ -773,7 +773,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>76.32</v>
+        <v>67.44</v>
       </c>
     </row>
     <row r="26">
@@ -781,7 +781,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>73.57</v>
+        <v>71.96</v>
       </c>
     </row>
     <row r="27">
@@ -789,7 +789,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>70.7</v>
+        <v>71.65</v>
       </c>
     </row>
     <row r="28">
@@ -797,7 +797,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>79.56</v>
+        <v>70.87</v>
       </c>
     </row>
     <row r="29">
@@ -805,7 +805,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>73.46</v>
+        <v>70.51</v>
       </c>
     </row>
     <row r="30">
@@ -813,7 +813,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>73.21</v>
+        <v>75.49</v>
       </c>
     </row>
     <row r="31">
@@ -821,7 +821,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>72.15</v>
+        <v>74.45</v>
       </c>
     </row>
     <row r="32">
@@ -829,7 +829,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>75.47</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="33">
@@ -837,7 +837,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>76.57</v>
+        <v>78.42</v>
       </c>
     </row>
     <row r="34">
@@ -845,7 +845,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>74.45</v>
+        <v>73.53</v>
       </c>
     </row>
     <row r="35">
@@ -853,7 +853,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>74.22</v>
+        <v>72.54</v>
       </c>
     </row>
     <row r="36">
@@ -861,7 +861,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>75.49</v>
+        <v>72.97</v>
       </c>
     </row>
     <row r="37">
@@ -869,7 +869,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>72.91</v>
+        <v>74.04</v>
       </c>
     </row>
     <row r="38">
@@ -877,7 +877,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>67.04</v>
+        <v>72.61</v>
       </c>
     </row>
     <row r="39">
@@ -885,7 +885,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>67.44</v>
+        <v>73.21</v>
       </c>
     </row>
     <row r="40">
@@ -893,7 +893,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>71.96</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="41">
@@ -901,7 +901,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>72.97</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="42">
@@ -909,7 +909,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>71.65</v>
+        <v>74.68</v>
       </c>
     </row>
     <row r="43">
@@ -917,7 +917,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>74.3</v>
+        <v>73.57</v>
       </c>
     </row>
     <row r="44">
@@ -925,7 +925,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>70.87</v>
+        <v>72.86</v>
       </c>
     </row>
     <row r="45">
@@ -933,7 +933,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>72.86</v>
+        <v>73.89</v>
       </c>
     </row>
     <row r="46">
@@ -941,7 +941,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>70.51</v>
+        <v>72.98</v>
       </c>
     </row>
     <row r="47">
@@ -949,7 +949,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>59.64</v>
+        <v>74.17</v>
       </c>
     </row>
     <row r="48">
@@ -957,7 +957,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>73.89</v>
+        <v>73.46</v>
       </c>
     </row>
     <row r="49">
@@ -965,7 +965,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>72.54</v>
+        <v>75.47</v>
       </c>
     </row>
   </sheetData>
